--- a/pages/Kierin_Points_Women.xlsx
+++ b/pages/Kierin_Points_Women.xlsx
@@ -1093,13 +1093,13 @@
     <t>02 Oct 2022</t>
   </si>
   <si>
-    <t>UCI World Championships</t>
-  </si>
-  <si>
-    <t>Nations' Cup</t>
-  </si>
-  <si>
-    <t>Continental Championships</t>
+    <t>WCh</t>
+  </si>
+  <si>
+    <t>NCp</t>
+  </si>
+  <si>
+    <t>CCh</t>
   </si>
   <si>
     <t>TCL General Ranking</t>
@@ -1108,16 +1108,16 @@
     <t>TCL Round Ranking</t>
   </si>
   <si>
-    <t>National Championships</t>
-  </si>
-  <si>
-    <t>Class 1</t>
+    <t>NCh</t>
+  </si>
+  <si>
+    <t>CL1</t>
   </si>
   <si>
     <t>National</t>
   </si>
   <si>
-    <t>Class 2</t>
+    <t>CL2</t>
   </si>
   <si>
     <t>Tissot UCI Track World Championships - Women Elite - Keirin - General Classification</t>

--- a/pages/Kierin_Points_Women.xlsx
+++ b/pages/Kierin_Points_Women.xlsx
@@ -367,7 +367,7 @@
     <t>THOMAS Lowri (TIN)</t>
   </si>
   <si>
-    <t>WANG Sin Ting</t>
+    <t>王WANG 歆婷sin Ting</t>
   </si>
   <si>
     <t>GUO Yufang</t>
